--- a/outputs/01a0b000-cf04-7f00-a568-1f20935b5dd8/vgb-property-calculation-basic-v0.10.0-rescored.xlsx
+++ b/outputs/01a0b000-cf04-7f00-a568-1f20935b5dd8/vgb-property-calculation-basic-v0.10.0-rescored.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="1" r:id="R157fc21eaf934cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="1" r:id="Rd34eb7ca068a4364"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -108,7 +108,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="24">
+  <x:fills count="29">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -225,8 +225,33 @@
         <x:fgColor rgb="FF000080"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4B5563"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5E7EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F4F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD1D5DB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="12">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -370,13 +395,41 @@
         <x:color rgb="FF008000"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9CA3AF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF9CA3AF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9CA3AF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9CA3AF"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <x:alignment vertical="bottom"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="223">
+  <x:cellXfs count="261">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="bottom"/>
     </x:xf>
@@ -1043,6 +1096,120 @@
     </x:xf>
     <x:xf numFmtId="165" fontId="8" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="25" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="26" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="25" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="25" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="8" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="25" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1287,1910 +1454,1910 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="123" customFormat="1" ht="24" customHeight="1">
-      <x:c r="A1" s="139" t="str">
+      <x:c r="A1" s="224" t="str">
         <x:v>表格 1</x:v>
       </x:c>
-      <x:c r="B1" s="139"/>
-      <x:c r="C1" s="139"/>
-      <x:c r="D1" s="139"/>
-      <x:c r="E1" s="139"/>
-      <x:c r="F1" s="139"/>
-      <x:c r="G1" s="139"/>
-      <x:c r="H1" s="139"/>
-      <x:c r="I1" s="139"/>
-      <x:c r="J1" s="139"/>
-      <x:c r="K1" s="139"/>
+      <x:c r="B1" s="224"/>
+      <x:c r="C1" s="224"/>
+      <x:c r="D1" s="224"/>
+      <x:c r="E1" s="224"/>
+      <x:c r="F1" s="224"/>
+      <x:c r="G1" s="224"/>
+      <x:c r="H1" s="224"/>
+      <x:c r="I1" s="224"/>
+      <x:c r="J1" s="224"/>
+      <x:c r="K1" s="224"/>
     </x:row>
     <x:row r="2" s="123" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A2" s="147" t="str">
+      <x:c r="A2" s="227" t="str">
         <x:v>题目 ID + 一句话概括</x:v>
       </x:c>
-      <x:c r="B2" s="147" t="str">
+      <x:c r="B2" s="227" t="str">
         <x:v>v0.10.0 容差范围</x:v>
       </x:c>
-      <x:c r="C2" s="147" t="str">
+      <x:c r="C2" s="227" t="str">
         <x:v>本题的标准答案</x:v>
       </x:c>
-      <x:c r="D2" s="147" t="str">
+      <x:c r="D2" s="227" t="str">
         <x:v>gpt-5-6-sol</x:v>
       </x:c>
-      <x:c r="E2" s="147"/>
-      <x:c r="F2" s="147" t="str">
+      <x:c r="E2" s="227"/>
+      <x:c r="F2" s="227" t="str">
         <x:v>gpt-5-6-sol</x:v>
       </x:c>
-      <x:c r="G2" s="147"/>
-      <x:c r="H2" s="147" t="str">
+      <x:c r="G2" s="227"/>
+      <x:c r="H2" s="227" t="str">
         <x:v>qwen3-8-flash</x:v>
       </x:c>
-      <x:c r="I2" s="147"/>
-      <x:c r="J2" s="147" t="str">
+      <x:c r="I2" s="227"/>
+      <x:c r="J2" s="227" t="str">
         <x:v>qwen3-8-flash</x:v>
       </x:c>
-      <x:c r="K2" s="147"/>
+      <x:c r="K2" s="227"/>
     </x:row>
     <x:row r="3" s="123" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A3" s="154"/>
-      <x:c r="B3" s="154"/>
-      <x:c r="C3" s="154"/>
-      <x:c r="D3" s="161" t="str">
+      <x:c r="A3" s="231"/>
+      <x:c r="B3" s="231"/>
+      <x:c r="C3" s="231"/>
+      <x:c r="D3" s="231" t="str">
         <x:v>skill-on</x:v>
       </x:c>
-      <x:c r="E3" s="161"/>
-      <x:c r="F3" s="161" t="str">
+      <x:c r="E3" s="231"/>
+      <x:c r="F3" s="231" t="str">
         <x:v>skill-off</x:v>
       </x:c>
-      <x:c r="G3" s="161"/>
-      <x:c r="H3" s="161" t="str">
+      <x:c r="G3" s="231"/>
+      <x:c r="H3" s="231" t="str">
         <x:v>skill-on</x:v>
       </x:c>
-      <x:c r="I3" s="161"/>
-      <x:c r="J3" s="161" t="str">
+      <x:c r="I3" s="231"/>
+      <x:c r="J3" s="231" t="str">
         <x:v>skill-off</x:v>
       </x:c>
-      <x:c r="K3" s="161"/>
+      <x:c r="K3" s="231"/>
     </x:row>
     <x:row r="4" s="123" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A4" s="154"/>
-      <x:c r="B4" s="154"/>
-      <x:c r="C4" s="154"/>
-      <x:c r="D4" s="171" t="str">
+      <x:c r="A4" s="237"/>
+      <x:c r="B4" s="237"/>
+      <x:c r="C4" s="237"/>
+      <x:c r="D4" s="237" t="str">
         <x:v>作答结果</x:v>
       </x:c>
-      <x:c r="E4" s="171" t="str">
+      <x:c r="E4" s="237" t="str">
         <x:v>v0.10.0 得分</x:v>
       </x:c>
-      <x:c r="F4" s="171" t="str">
+      <x:c r="F4" s="237" t="str">
         <x:v>作答结果</x:v>
       </x:c>
-      <x:c r="G4" s="171" t="str">
+      <x:c r="G4" s="237" t="str">
         <x:v>v0.10.0 得分</x:v>
       </x:c>
-      <x:c r="H4" s="171" t="str">
+      <x:c r="H4" s="237" t="str">
         <x:v>作答结果</x:v>
       </x:c>
-      <x:c r="I4" s="171" t="str">
+      <x:c r="I4" s="237" t="str">
         <x:v>v0.10.0 得分</x:v>
       </x:c>
-      <x:c r="J4" s="171" t="str">
+      <x:c r="J4" s="237" t="str">
         <x:v>作答结果</x:v>
       </x:c>
-      <x:c r="K4" s="171" t="str">
+      <x:c r="K4" s="237" t="str">
         <x:v>v0.10.0 得分</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A5" s="181" t="str">
+      <x:c r="A5" s="244" t="str">
         <x:v>property_calculation_basic_001_toluene_aqueous_solvation_free_energy；概括：计算甲苯的水相溶剂化自由能。</x:v>
       </x:c>
-      <x:c r="B5" s="181" t="str">
+      <x:c r="B5" s="244" t="str">
         <x:v>±3 kcal/mol</x:v>
       </x:c>
-      <x:c r="C5" s="181" t="str">
+      <x:c r="C5" s="244" t="str">
         <x:v>{"answer":-0.82,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D5" s="189" t="str">
+      <x:c r="D5" s="248" t="str">
         <x:v>{"answer":-0.832,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E5" s="194" t="n">
+      <x:c r="E5" s="251" t="n">
         <x:v>0.996</x:v>
       </x:c>
-      <x:c r="F5" s="189" t="str">
+      <x:c r="F5" s="248" t="str">
         <x:v>{"answer":0.17,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G5" s="194" t="n">
+      <x:c r="G5" s="251" t="n">
         <x:v>0.6699999999999999</x:v>
       </x:c>
-      <x:c r="H5" s="189" t="str">
+      <x:c r="H5" s="248" t="str">
         <x:v>{"answer":-0.83,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I5" s="194" t="n">
+      <x:c r="I5" s="251" t="n">
         <x:v>0.9966666666666667</x:v>
       </x:c>
-      <x:c r="J5" s="189" t="str">
+      <x:c r="J5" s="248" t="str">
         <x:v>{"answer":-0.68,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K5" s="194" t="n">
+      <x:c r="K5" s="251" t="n">
         <x:v>0.9533333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A6" s="181" t="str">
+      <x:c r="A6" s="244" t="str">
         <x:v>property_calculation_basic_002_ethanol_aqueous_solvation_free_energy；概括：计算乙醇的水相溶剂化自由能。</x:v>
       </x:c>
-      <x:c r="B6" s="184" t="str">
+      <x:c r="B6" s="245" t="str">
         <x:v>±3 kcal/mol</x:v>
       </x:c>
-      <x:c r="C6" s="181" t="str">
+      <x:c r="C6" s="244" t="str">
         <x:v>{"answer":-5.42,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D6" s="189" t="str">
+      <x:c r="D6" s="248" t="str">
         <x:v>{"answer":-5.01,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E6" s="194" t="n">
+      <x:c r="E6" s="251" t="n">
         <x:v>0.8633333333333333</x:v>
       </x:c>
-      <x:c r="F6" s="189" t="str">
+      <x:c r="F6" s="248" t="str">
         <x:v>{"answer":-5.01,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G6" s="194" t="n">
+      <x:c r="G6" s="251" t="n">
         <x:v>0.8633333333333333</x:v>
       </x:c>
-      <x:c r="H6" s="189" t="str">
+      <x:c r="H6" s="248" t="str">
         <x:v>{"answer":-5.87,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I6" s="194" t="n">
+      <x:c r="I6" s="251" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="J6" s="189" t="str">
+      <x:c r="J6" s="248" t="str">
         <x:v>{"answer":-4.97,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K6" s="194" t="n">
+      <x:c r="K6" s="251" t="n">
         <x:v>0.85</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A7" s="181" t="str">
+      <x:c r="A7" s="244" t="str">
         <x:v>property_calculation_basic_003_diethyl_ether_aqueous_solvation_free_energy；概括：计算乙醚的水相溶剂化自由能。</x:v>
       </x:c>
-      <x:c r="B7" s="181" t="str">
+      <x:c r="B7" s="244" t="str">
         <x:v>±3 kcal/mol</x:v>
       </x:c>
-      <x:c r="C7" s="181" t="str">
+      <x:c r="C7" s="244" t="str">
         <x:v>{"answer":-2.11,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D7" s="189" t="str">
+      <x:c r="D7" s="248" t="str">
         <x:v>{"answer":-1.76,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E7" s="194" t="n">
+      <x:c r="E7" s="251" t="n">
         <x:v>0.8833333333333334</x:v>
       </x:c>
-      <x:c r="F7" s="189" t="str">
+      <x:c r="F7" s="248" t="str">
         <x:v>{"answer":-3.37,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G7" s="194" t="n">
+      <x:c r="G7" s="251" t="n">
         <x:v>0.5799999999999998</x:v>
       </x:c>
-      <x:c r="H7" s="189" t="str">
+      <x:c r="H7" s="248" t="str">
         <x:v>{"answer":-2.0,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I7" s="194" t="n">
+      <x:c r="I7" s="251" t="n">
         <x:v>0.9633333333333334</x:v>
       </x:c>
-      <x:c r="J7" s="189" t="str">
+      <x:c r="J7" s="248" t="str">
         <x:v>{"answer":-4.3,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K7" s="194" t="n">
+      <x:c r="K7" s="251" t="n">
         <x:v>0.27</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A8" s="181" t="str">
+      <x:c r="A8" s="244" t="str">
         <x:v>property_calculation_basic_004_anisole_aqueous_solvation_free_energy；概括：计算苯甲醚的水相溶剂化自由能。</x:v>
       </x:c>
-      <x:c r="B8" s="181" t="str">
+      <x:c r="B8" s="244" t="str">
         <x:v>±3 kcal/mol</x:v>
       </x:c>
-      <x:c r="C8" s="181" t="str">
+      <x:c r="C8" s="244" t="str">
         <x:v>{"answer":-1.98,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D8" s="189" t="str">
+      <x:c r="D8" s="248" t="str">
         <x:v>{"answer":-1.963488,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E8" s="194" t="n">
+      <x:c r="E8" s="251" t="n">
         <x:v>0.9944959999999999</x:v>
       </x:c>
-      <x:c r="F8" s="189" t="str">
+      <x:c r="F8" s="248" t="str">
         <x:v>{"answer":-3.26,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G8" s="194" t="n">
+      <x:c r="G8" s="251" t="n">
         <x:v>0.5733333333333335</x:v>
       </x:c>
-      <x:c r="H8" s="189" t="str">
+      <x:c r="H8" s="248" t="str">
         <x:v>{"answer":-1.98,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I8" s="194" t="n">
+      <x:c r="I8" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="189" t="str">
+      <x:c r="J8" s="248" t="str">
         <x:v>{"answer":-2.05,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K8" s="194" t="n">
+      <x:c r="K8" s="251" t="n">
         <x:v>0.9766666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A9" s="181" t="str">
+      <x:c r="A9" s="244" t="str">
         <x:v>property_calculation_basic_005_nitrobenzene_reduction_potential；概括：计算硝基苯在乙腈中相对于 SCE 的第一次还原电位。</x:v>
       </x:c>
-      <x:c r="B9" s="181" t="str">
+      <x:c r="B9" s="244" t="str">
         <x:v>±0.5 V</x:v>
       </x:c>
-      <x:c r="C9" s="181" t="str">
+      <x:c r="C9" s="244" t="str">
         <x:v>{"answer":-1.24,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="D9" s="189" t="str">
+      <x:c r="D9" s="248" t="str">
         <x:v>{"answer":-1.15,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="E9" s="194" t="n">
+      <x:c r="E9" s="251" t="n">
         <x:v>0.8199999999999998</x:v>
       </x:c>
-      <x:c r="F9" s="189" t="str">
+      <x:c r="F9" s="248" t="str">
         <x:v>{"answer":-1.16,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="G9" s="194" t="n">
+      <x:c r="G9" s="251" t="n">
         <x:v>0.8399999999999999</x:v>
       </x:c>
-      <x:c r="H9" s="189" t="str">
+      <x:c r="H9" s="248" t="str">
         <x:v>{"answer":-1.38,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="I9" s="194" t="n">
+      <x:c r="I9" s="251" t="n">
         <x:v>0.7200000000000002</x:v>
       </x:c>
-      <x:c r="J9" s="189" t="str">
+      <x:c r="J9" s="248" t="str">
         <x:v>{"answer":-1.14,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="K9" s="194" t="n">
+      <x:c r="K9" s="251" t="n">
         <x:v>0.7999999999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A10" s="181" t="str">
+      <x:c r="A10" s="244" t="str">
         <x:v>property_calculation_basic_006_tetracyanoethylene_reduction_potential；概括：计算四氰基乙烯在乙腈中相对于 SCE 的第一次还原电位。</x:v>
       </x:c>
-      <x:c r="B10" s="181" t="str">
+      <x:c r="B10" s="244" t="str">
         <x:v>±0.5 V</x:v>
       </x:c>
-      <x:c r="C10" s="181" t="str">
+      <x:c r="C10" s="244" t="str">
         <x:v>{"answer":0.21,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="D10" s="189" t="str">
+      <x:c r="D10" s="248" t="str">
         <x:v>{"answer":0.14,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="E10" s="194" t="n">
+      <x:c r="E10" s="251" t="n">
         <x:v>0.8600000000000001</x:v>
       </x:c>
-      <x:c r="F10" s="189" t="str">
+      <x:c r="F10" s="248" t="str">
         <x:v>{"answer":0.24,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="G10" s="194" t="n">
+      <x:c r="G10" s="251" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="H10" s="189" t="str">
+      <x:c r="H10" s="248" t="str">
         <x:v>{"answer":-0.34,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="I10" s="194" t="n">
+      <x:c r="I10" s="251" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="189" t="str">
+      <x:c r="J10" s="248" t="str">
         <x:v>{"answer":0.14,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="K10" s="194" t="n">
+      <x:c r="K10" s="251" t="n">
         <x:v>0.8600000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A11" s="181" t="str">
+      <x:c r="A11" s="244" t="str">
         <x:v>property_calculation_basic_007_dimethylaniline_oxidation_potential；概括：计算二甲基苯胺在乙腈中相对于 SCE 的第一次氧化电位。</x:v>
       </x:c>
-      <x:c r="B11" s="181" t="str">
+      <x:c r="B11" s="244" t="str">
         <x:v>±0.5 V</x:v>
       </x:c>
-      <x:c r="C11" s="181" t="str">
+      <x:c r="C11" s="244" t="str">
         <x:v>{"answer":0.83,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="D11" s="189" t="str">
+      <x:c r="D11" s="248" t="str">
         <x:v>{"answer":0.81,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="E11" s="194" t="n">
+      <x:c r="E11" s="251" t="n">
         <x:v>0.9600000000000002</x:v>
       </x:c>
-      <x:c r="F11" s="189" t="str">
+      <x:c r="F11" s="248" t="str">
         <x:v>{"answer":0.72,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="G11" s="194" t="n">
+      <x:c r="G11" s="251" t="n">
         <x:v>0.78</x:v>
       </x:c>
-      <x:c r="H11" s="189" t="str">
+      <x:c r="H11" s="248" t="str">
         <x:v>{"answer":0.99,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="I11" s="194" t="n">
+      <x:c r="I11" s="251" t="n">
         <x:v>0.6799999999999999</x:v>
       </x:c>
-      <x:c r="J11" s="189" t="str">
+      <x:c r="J11" s="248" t="str">
         <x:v>{"answer":0.86,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="K11" s="194" t="n">
+      <x:c r="K11" s="251" t="n">
         <x:v>0.94</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A12" s="181" t="str">
+      <x:c r="A12" s="244" t="str">
         <x:v>property_calculation_basic_008_triphenylamine_oxidation_potential；概括：计算三苯胺在乙腈中相对于 SCE 的第一次氧化电位。</x:v>
       </x:c>
-      <x:c r="B12" s="181" t="str">
+      <x:c r="B12" s="244" t="str">
         <x:v>±0.5 V</x:v>
       </x:c>
-      <x:c r="C12" s="181" t="str">
+      <x:c r="C12" s="244" t="str">
         <x:v>{"answer":0.82,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="D12" s="189" t="str">
+      <x:c r="D12" s="248" t="str">
         <x:v>{"answer":0.85,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="E12" s="194" t="n">
+      <x:c r="E12" s="251" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="F12" s="189" t="str">
+      <x:c r="F12" s="248" t="str">
         <x:v>{"answer":0.86,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="G12" s="194" t="n">
+      <x:c r="G12" s="251" t="n">
         <x:v>0.9199999999999999</x:v>
       </x:c>
-      <x:c r="H12" s="189" t="str">
+      <x:c r="H12" s="248" t="str">
         <x:v>{"answer":0.88,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="I12" s="194" t="n">
+      <x:c r="I12" s="251" t="n">
         <x:v>0.8799999999999999</x:v>
       </x:c>
-      <x:c r="J12" s="189" t="str">
+      <x:c r="J12" s="248" t="str">
         <x:v>{"answer":0.85,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="K12" s="194" t="n">
+      <x:c r="K12" s="251" t="n">
         <x:v>0.94</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A13" s="181" t="str">
+      <x:c r="A13" s="244" t="str">
         <x:v>property_calculation_basic_009_thianthrene_oxidation_potential；概括：计算噻蒽在乙腈中相对于 SCE 的第一次氧化电位。</x:v>
       </x:c>
-      <x:c r="B13" s="181" t="str">
+      <x:c r="B13" s="244" t="str">
         <x:v>±0.5 V</x:v>
       </x:c>
-      <x:c r="C13" s="181" t="str">
+      <x:c r="C13" s="244" t="str">
         <x:v>{"answer":1.11,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="D13" s="189" t="str">
+      <x:c r="D13" s="248" t="str">
         <x:v>{"answer":0.86,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="E13" s="194" t="n">
+      <x:c r="E13" s="251" t="n">
         <x:v>0.4999999999999998</x:v>
       </x:c>
-      <x:c r="F13" s="189" t="str">
+      <x:c r="F13" s="248" t="str">
         <x:v>{"answer":0.93,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="G13" s="194" t="n">
+      <x:c r="G13" s="251" t="n">
         <x:v>0.6399999999999999</x:v>
       </x:c>
-      <x:c r="H13" s="189" t="str">
+      <x:c r="H13" s="248" t="str">
         <x:v>{"answer":1.06,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="I13" s="194" t="n">
+      <x:c r="I13" s="251" t="n">
         <x:v>0.8999999999999999</x:v>
       </x:c>
-      <x:c r="J13" s="189" t="str">
+      <x:c r="J13" s="248" t="str">
         <x:v>{"answer":0.93,"unit":"V"}</x:v>
       </x:c>
-      <x:c r="K13" s="194" t="n">
+      <x:c r="K13" s="251" t="n">
         <x:v>0.6399999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A14" s="181" t="str">
+      <x:c r="A14" s="244" t="str">
         <x:v>property_calculation_basic_010_water_dimer_binding_energy；概括：计算氢键水二聚体的结合能并保留符号。</x:v>
       </x:c>
-      <x:c r="B14" s="181" t="str">
+      <x:c r="B14" s="244" t="str">
         <x:v>±2 kcal/mol</x:v>
       </x:c>
-      <x:c r="C14" s="181" t="str">
+      <x:c r="C14" s="244" t="str">
         <x:v>{"answer":-4.97,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D14" s="189" t="str">
+      <x:c r="D14" s="248" t="str">
         <x:v>{"answer":-5.02,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E14" s="194" t="n">
+      <x:c r="E14" s="251" t="n">
         <x:v>0.9750000000000001</x:v>
       </x:c>
-      <x:c r="F14" s="189" t="str">
+      <x:c r="F14" s="248" t="str">
         <x:v>{"answer":-5.02,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G14" s="194" t="n">
+      <x:c r="G14" s="251" t="n">
         <x:v>0.9750000000000001</x:v>
       </x:c>
-      <x:c r="H14" s="189" t="str">
+      <x:c r="H14" s="248" t="str">
         <x:v>{"answer":-4.4,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I14" s="194" t="n">
+      <x:c r="I14" s="251" t="n">
         <x:v>0.7150000000000003</x:v>
       </x:c>
-      <x:c r="J14" s="189" t="str">
+      <x:c r="J14" s="248" t="str">
         <x:v>{"answer":-5.0,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K14" s="194" t="n">
+      <x:c r="K14" s="251" t="n">
         <x:v>0.9849999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A15" s="181" t="str">
+      <x:c r="A15" s="244" t="str">
         <x:v>property_calculation_basic_011_ammonia_dimer_binding_energy；概括：计算氢键氨二聚体的结合能并保留符号。</x:v>
       </x:c>
-      <x:c r="B15" s="181" t="str">
+      <x:c r="B15" s="244" t="str">
         <x:v>±2 kcal/mol</x:v>
       </x:c>
-      <x:c r="C15" s="181" t="str">
+      <x:c r="C15" s="244" t="str">
         <x:v>{"answer":-2.85,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D15" s="189" t="str">
+      <x:c r="D15" s="248" t="str">
         <x:v>{"answer":-1.7621272831,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E15" s="194" t="n">
+      <x:c r="E15" s="251" t="n">
         <x:v>0.45606364155</x:v>
       </x:c>
-      <x:c r="F15" s="189" t="str">
+      <x:c r="F15" s="248" t="str">
         <x:v>{"answer":-3.17,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G15" s="194" t="n">
+      <x:c r="G15" s="251" t="n">
         <x:v>0.8400000000000001</x:v>
       </x:c>
-      <x:c r="H15" s="189" t="str">
+      <x:c r="H15" s="248" t="str">
         <x:v>{"answer":-2.85,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I15" s="194" t="n">
+      <x:c r="I15" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J15" s="189" t="str">
+      <x:c r="J15" s="248" t="str">
         <x:v>{"answer":-2.85,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K15" s="194" t="n">
+      <x:c r="K15" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A16" s="181" t="str">
+      <x:c r="A16" s="244" t="str">
         <x:v>property_calculation_basic_012_benzene_t_dimer_binding_energy；概括：计算 T 形苯二聚体的结合能并保留符号。</x:v>
       </x:c>
-      <x:c r="B16" s="181" t="str">
+      <x:c r="B16" s="244" t="str">
         <x:v>±2 kcal/mol</x:v>
       </x:c>
-      <x:c r="C16" s="181" t="str">
+      <x:c r="C16" s="244" t="str">
         <x:v>{"answer":-2.48,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D16" s="189" t="str">
+      <x:c r="D16" s="248" t="str">
         <x:v>{"answer":-2.74,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E16" s="194" t="n">
+      <x:c r="E16" s="251" t="n">
         <x:v>0.8699999999999999</x:v>
       </x:c>
-      <x:c r="F16" s="189" t="str">
+      <x:c r="F16" s="248" t="str">
         <x:v>{"answer":-2.74,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G16" s="194" t="n">
+      <x:c r="G16" s="251" t="n">
         <x:v>0.8699999999999999</x:v>
       </x:c>
-      <x:c r="H16" s="189" t="str">
+      <x:c r="H16" s="248" t="str">
         <x:v>{"answer":-2.25,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I16" s="194" t="n">
+      <x:c r="I16" s="251" t="n">
         <x:v>0.885</x:v>
       </x:c>
-      <x:c r="J16" s="189" t="str">
+      <x:c r="J16" s="248" t="str">
         <x:v>{"answer":-2.4,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K16" s="194" t="n">
+      <x:c r="K16" s="251" t="n">
         <x:v>0.96</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A17" s="181" t="str">
+      <x:c r="A17" s="244" t="str">
         <x:v>property_calculation_basic_013_adenine_thymine_wc_pair_binding_energy；概括：计算 Watson-Crick 腺嘌呤-胸腺嘧啶碱基对的结合能并保留符号。</x:v>
       </x:c>
-      <x:c r="B17" s="181" t="str">
+      <x:c r="B17" s="244" t="str">
         <x:v>±3 kcal/mol</x:v>
       </x:c>
-      <x:c r="C17" s="181" t="str">
+      <x:c r="C17" s="244" t="str">
         <x:v>{"answer":-16.13,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D17" s="189" t="str">
+      <x:c r="D17" s="248" t="str">
         <x:v>{"answer":-16.37,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E17" s="194" t="n">
+      <x:c r="E17" s="251" t="n">
         <x:v>0.9199999999999994</x:v>
       </x:c>
-      <x:c r="F17" s="189" t="str">
+      <x:c r="F17" s="248" t="str">
         <x:v>{"answer":-16.37,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G17" s="194" t="n">
+      <x:c r="G17" s="251" t="n">
         <x:v>0.9199999999999994</x:v>
       </x:c>
-      <x:c r="H17" s="189" t="str">
+      <x:c r="H17" s="248" t="str">
         <x:v>{"answer":-16.13,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I17" s="194" t="n">
+      <x:c r="I17" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J17" s="189" t="str">
+      <x:c r="J17" s="248" t="str">
         <x:v>{"answer":-16.47,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K17" s="194" t="n">
+      <x:c r="K17" s="251" t="n">
         <x:v>0.8866666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A18" s="181" t="str">
+      <x:c r="A18" s="244" t="str">
         <x:v>property_calculation_basic_014_water_methanol_complex_binding_energy；概括：计算氢键水-甲醇复合物的结合能并保留符号。</x:v>
       </x:c>
-      <x:c r="B18" s="181" t="str">
+      <x:c r="B18" s="244" t="str">
         <x:v>±2 kcal/mol</x:v>
       </x:c>
-      <x:c r="C18" s="181" t="str">
+      <x:c r="C18" s="244" t="str">
         <x:v>{"answer":-4.89,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D18" s="189" t="str">
+      <x:c r="D18" s="248" t="str">
         <x:v>{"answer":-5.11,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E18" s="194" t="n">
+      <x:c r="E18" s="251" t="n">
         <x:v>0.8899999999999997</x:v>
       </x:c>
-      <x:c r="F18" s="189" t="str">
+      <x:c r="F18" s="248" t="str">
         <x:v>{"answer":-5.11,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G18" s="194" t="n">
+      <x:c r="G18" s="251" t="n">
         <x:v>0.8899999999999997</x:v>
       </x:c>
-      <x:c r="H18" s="189" t="str">
+      <x:c r="H18" s="248" t="str">
         <x:v>{"answer":-4.87,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I18" s="194" t="n">
+      <x:c r="I18" s="251" t="n">
         <x:v>0.9900000000000002</x:v>
       </x:c>
-      <x:c r="J18" s="189" t="str">
+      <x:c r="J18" s="248" t="str">
         <x:v>{"answer":-4.96,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K18" s="194" t="n">
+      <x:c r="K18" s="251" t="n">
         <x:v>0.9649999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A19" s="181" t="str">
+      <x:c r="A19" s="244" t="str">
         <x:v>property_calculation_basic_015_ethene_ethyne_t_complex_binding_energy；概括：计算 T 形乙烯-乙炔复合物的结合能并保留符号。</x:v>
       </x:c>
-      <x:c r="B19" s="181" t="str">
+      <x:c r="B19" s="244" t="str">
         <x:v>±2 kcal/mol</x:v>
       </x:c>
-      <x:c r="C19" s="181" t="str">
+      <x:c r="C19" s="244" t="str">
         <x:v>{"answer":-1.33,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D19" s="189" t="str">
+      <x:c r="D19" s="248" t="str">
         <x:v>{"answer":0.784,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E19" s="194" t="n">
+      <x:c r="E19" s="251" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="189" t="str">
+      <x:c r="F19" s="248" t="str">
         <x:v>{"answer":-1.53,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G19" s="194" t="n">
+      <x:c r="G19" s="251" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="H19" s="189" t="str">
+      <x:c r="H19" s="248" t="str">
         <x:v>{"answer":-1.33,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I19" s="194" t="n">
+      <x:c r="I19" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J19" s="189" t="str">
+      <x:c r="J19" s="248" t="str">
         <x:v>{"answer":-1.33,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K19" s="194" t="n">
+      <x:c r="K19" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A20" s="181" t="str">
+      <x:c r="A20" s="244" t="str">
         <x:v>property_calculation_basic_016_thiophene_polarizability；概括：计算 GFN2-xTB 水平下噻吩的静态平均极化率。</x:v>
       </x:c>
-      <x:c r="B20" s="181" t="str">
+      <x:c r="B20" s="244" t="str">
         <x:v>±20%</x:v>
       </x:c>
-      <x:c r="C20" s="181" t="str">
+      <x:c r="C20" s="244" t="str">
         <x:v>{"answer":65.01,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="D20" s="189" t="str">
+      <x:c r="D20" s="248" t="str">
         <x:v>{"answer":65.014425,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="E20" s="194" t="n">
+      <x:c r="E20" s="251" t="n">
         <x:v>0.9996596677434243</x:v>
       </x:c>
-      <x:c r="F20" s="189" t="str">
+      <x:c r="F20" s="248" t="str">
         <x:v>{"answer":65.014427,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="G20" s="194" t="n">
+      <x:c r="G20" s="251" t="n">
         <x:v>0.9996595139209358</x:v>
       </x:c>
-      <x:c r="H20" s="189" t="str">
+      <x:c r="H20" s="248" t="str">
         <x:v>{"answer":65.0135,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="I20" s="194" t="n">
+      <x:c r="I20" s="251" t="n">
         <x:v>0.9997308106445171</x:v>
       </x:c>
-      <x:c r="J20" s="189" t="str">
+      <x:c r="J20" s="248" t="str">
         <x:v>{"answer":65.014,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="K20" s="194" t="n">
+      <x:c r="K20" s="251" t="n">
         <x:v>0.999692355022305</x:v>
       </x:c>
     </x:row>
     <x:row r="21" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A21" s="181" t="str">
+      <x:c r="A21" s="244" t="str">
         <x:v>property_calculation_basic_017_benzene_polarizability；概括：计算 GFN2-xTB 水平下苯的静态平均极化率。</x:v>
       </x:c>
-      <x:c r="B21" s="181" t="str">
+      <x:c r="B21" s="244" t="str">
         <x:v>±20%</x:v>
       </x:c>
-      <x:c r="C21" s="181" t="str">
+      <x:c r="C21" s="244" t="str">
         <x:v>{"answer":67.87,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="D21" s="189" t="str">
+      <x:c r="D21" s="248" t="str">
         <x:v>{"answer":58.9073,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="E21" s="194" t="n">
+      <x:c r="E21" s="251" t="n">
         <x:v>0.33971563282746386</x:v>
       </x:c>
-      <x:c r="F21" s="189" t="str">
+      <x:c r="F21" s="248" t="str">
         <x:v>{"answer":67.869889,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="G21" s="194" t="n">
+      <x:c r="G21" s="251" t="n">
         <x:v>0.999991822602033</x:v>
       </x:c>
-      <x:c r="H21" s="189" t="str">
+      <x:c r="H21" s="248" t="str">
         <x:v>{"answer":67.8696,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="I21" s="194" t="n">
+      <x:c r="I21" s="251" t="n">
         <x:v>0.9999705318992191</x:v>
       </x:c>
-      <x:c r="J21" s="189" t="str">
+      <x:c r="J21" s="248" t="str">
         <x:v>{"answer":67.87,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="K21" s="194" t="n">
+      <x:c r="K21" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A22" s="181" t="str">
+      <x:c r="A22" s="244" t="str">
         <x:v>property_calculation_basic_018_octatetraene_polarizability；概括：计算 GFN2-xTB 水平下辛四烯的静态平均极化率。</x:v>
       </x:c>
-      <x:c r="B22" s="181" t="str">
+      <x:c r="B22" s="244" t="str">
         <x:v>±20%</x:v>
       </x:c>
-      <x:c r="C22" s="181" t="str">
+      <x:c r="C22" s="244" t="str">
         <x:v>{"answer":95.51,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="D22" s="189" t="str">
+      <x:c r="D22" s="248" t="str">
         <x:v>{"answer":95.508492,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="E22" s="194" t="n">
+      <x:c r="E22" s="251" t="n">
         <x:v>0.9999210553868704</x:v>
       </x:c>
-      <x:c r="F22" s="189" t="str">
+      <x:c r="F22" s="248" t="str">
         <x:v>{"answer":95.531814,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="G22" s="194" t="n">
+      <x:c r="G22" s="251" t="n">
         <x:v>0.9988580253376614</x:v>
       </x:c>
-      <x:c r="H22" s="189" t="str">
+      <x:c r="H22" s="248" t="str">
         <x:v>{"answer":101.7,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="I22" s="194" t="n">
+      <x:c r="I22" s="251" t="n">
         <x:v>0.6759501622866717</x:v>
       </x:c>
-      <x:c r="J22" s="189" t="str">
+      <x:c r="J22" s="248" t="str">
         <x:v>{"answer":95.51,"unit":"a.u."}</x:v>
       </x:c>
-      <x:c r="K22" s="194" t="n">
+      <x:c r="K22" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A23" s="181" t="str">
+      <x:c r="A23" s="244" t="str">
         <x:v>property_calculation_basic_019_dimethyl_sulfoxide_water_dipole_moment；概括：计算 GFN2-xTB 水平下水中二甲基亚砜的偶极矩。</x:v>
       </x:c>
-      <x:c r="B23" s="181" t="str">
+      <x:c r="B23" s="244" t="str">
         <x:v>±20%</x:v>
       </x:c>
-      <x:c r="C23" s="181" t="str">
+      <x:c r="C23" s="244" t="str">
         <x:v>{"answer":5.43,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="D23" s="189" t="str">
+      <x:c r="D23" s="248" t="str">
         <x:v>{"answer":5.430,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="E23" s="194" t="n">
+      <x:c r="E23" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F23" s="189" t="str">
+      <x:c r="F23" s="248" t="str">
         <x:v>{"answer":5.431,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="G23" s="194" t="n">
+      <x:c r="G23" s="251" t="n">
         <x:v>0.9990791896869242</x:v>
       </x:c>
-      <x:c r="H23" s="189" t="str">
+      <x:c r="H23" s="248" t="str">
         <x:v>{"answer":5.433,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="I23" s="194" t="n">
+      <x:c r="I23" s="251" t="n">
         <x:v>0.9972375690607733</x:v>
       </x:c>
-      <x:c r="J23" s="189" t="str">
+      <x:c r="J23" s="248" t="str">
         <x:v>{"answer":5.434,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="K23" s="194" t="n">
+      <x:c r="K23" s="251" t="n">
         <x:v>0.9963167587476975</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A24" s="181" t="str">
+      <x:c r="A24" s="244" t="str">
         <x:v>property_calculation_basic_020_cis_dichloroethene_dipole_moment；概括：计算 GFN2-xTB 水平下气相顺式-1,2-二氯乙烯的偶极矩。</x:v>
       </x:c>
-      <x:c r="B24" s="181" t="str">
+      <x:c r="B24" s="244" t="str">
         <x:v>±20%</x:v>
       </x:c>
-      <x:c r="C24" s="181" t="str">
+      <x:c r="C24" s="244" t="str">
         <x:v>{"answer":1.88,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="D24" s="189" t="str">
+      <x:c r="D24" s="248" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="E24" s="194" t="n">
+      <x:c r="E24" s="251" t="n">
         <x:v>0.9946808510638298</x:v>
       </x:c>
-      <x:c r="F24" s="189" t="str">
+      <x:c r="F24" s="248" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="G24" s="194" t="n">
+      <x:c r="G24" s="251" t="n">
         <x:v>0.9946808510638298</x:v>
       </x:c>
-      <x:c r="H24" s="189" t="str">
+      <x:c r="H24" s="248" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="I24" s="194" t="n">
+      <x:c r="I24" s="251" t="n">
         <x:v>0.9946808510638298</x:v>
       </x:c>
-      <x:c r="J24" s="189" t="str">
+      <x:c r="J24" s="248" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="K24" s="194" t="n">
+      <x:c r="K24" s="251" t="n">
         <x:v>0.9946808510638298</x:v>
       </x:c>
     </x:row>
     <x:row r="25" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A25" s="181" t="str">
+      <x:c r="A25" s="244" t="str">
         <x:v>property_calculation_basic_021_acetonitrile_dipole_moment；概括：计算 GFN2-xTB 水平下气相乙腈的偶极矩。</x:v>
       </x:c>
-      <x:c r="B25" s="181" t="str">
+      <x:c r="B25" s="244" t="str">
         <x:v>±20%</x:v>
       </x:c>
-      <x:c r="C25" s="181" t="str">
+      <x:c r="C25" s="244" t="str">
         <x:v>{"answer":3.85,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="D25" s="189" t="str">
+      <x:c r="D25" s="248" t="str">
         <x:v>{"answer":3.852,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="E25" s="194" t="n">
+      <x:c r="E25" s="251" t="n">
         <x:v>0.9974025974025977</x:v>
       </x:c>
-      <x:c r="F25" s="189" t="str">
+      <x:c r="F25" s="248" t="str">
         <x:v>{"answer":3.852,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="G25" s="194" t="n">
+      <x:c r="G25" s="251" t="n">
         <x:v>0.9974025974025977</x:v>
       </x:c>
-      <x:c r="H25" s="189" t="str">
+      <x:c r="H25" s="248" t="str">
         <x:v>{"answer":3.851,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="I25" s="194" t="n">
+      <x:c r="I25" s="251" t="n">
         <x:v>0.9987012987012989</x:v>
       </x:c>
-      <x:c r="J25" s="189" t="str">
+      <x:c r="J25" s="248" t="str">
         <x:v>{"answer":3.85,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="K25" s="194" t="n">
+      <x:c r="K25" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A26" s="181" t="str">
+      <x:c r="A26" s="244" t="str">
         <x:v>property_calculation_basic_022_naphthalene_bridge_bond_order；概括：计算 GFN2-xTB 水平下萘桥头 C-C 键的 Wiberg 键级。</x:v>
       </x:c>
-      <x:c r="B26" s="181" t="str">
+      <x:c r="B26" s="244" t="str">
         <x:v>±0.2</x:v>
       </x:c>
-      <x:c r="C26" s="181" t="str">
+      <x:c r="C26" s="244" t="str">
         <x:v>{"answer":1.2522,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D26" s="189" t="str">
+      <x:c r="D26" s="248" t="str">
         <x:v>{"answer":1.252,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E26" s="194" t="n">
+      <x:c r="E26" s="251" t="n">
         <x:v>0.9990000000000001</x:v>
       </x:c>
-      <x:c r="F26" s="189" t="str">
+      <x:c r="F26" s="248" t="str">
         <x:v>{"answer":1.2522024,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G26" s="194" t="n">
+      <x:c r="G26" s="251" t="n">
         <x:v>0.9999879999999997</x:v>
       </x:c>
-      <x:c r="H26" s="189" t="str">
+      <x:c r="H26" s="248" t="str">
         <x:v>{"answer":1.2522,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I26" s="194" t="n">
+      <x:c r="I26" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="189" t="str">
+      <x:c r="J26" s="248" t="str">
         <x:v>{"answer":1.2523,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K26" s="194" t="n">
+      <x:c r="K26" s="251" t="n">
         <x:v>0.9995</x:v>
       </x:c>
     </x:row>
     <x:row r="27" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A27" s="181" t="str">
+      <x:c r="A27" s="244" t="str">
         <x:v>property_calculation_basic_023_dimethyl_sulfone_so_bond_order；概括：计算 GFN2-xTB 水平下二甲基砜指定 S-O 键的 Wiberg 键级。</x:v>
       </x:c>
-      <x:c r="B27" s="181" t="str">
+      <x:c r="B27" s="244" t="str">
         <x:v>±0.2</x:v>
       </x:c>
-      <x:c r="C27" s="181" t="str">
+      <x:c r="C27" s="244" t="str">
         <x:v>{"answer":1.6615,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D27" s="189" t="str">
+      <x:c r="D27" s="248" t="str">
         <x:v>{"answer":1.639,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E27" s="194" t="n">
+      <x:c r="E27" s="251" t="n">
         <x:v>0.8875000000000002</x:v>
       </x:c>
-      <x:c r="F27" s="189" t="str">
+      <x:c r="F27" s="248" t="str">
         <x:v>{"answer":1.6615304058,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G27" s="194" t="n">
+      <x:c r="G27" s="251" t="n">
         <x:v>0.9998479709999999</x:v>
       </x:c>
-      <x:c r="H27" s="189" t="str">
+      <x:c r="H27" s="248" t="str">
         <x:v>{"answer":1.6614,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I27" s="194" t="n">
+      <x:c r="I27" s="251" t="n">
         <x:v>0.9995</x:v>
       </x:c>
-      <x:c r="J27" s="189" t="str">
+      <x:c r="J27" s="248" t="str">
         <x:v>{"answer":1.6614,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K27" s="194" t="n">
+      <x:c r="K27" s="251" t="n">
         <x:v>0.9995</x:v>
       </x:c>
     </x:row>
     <x:row r="28" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A28" s="181" t="str">
+      <x:c r="A28" s="244" t="str">
         <x:v>property_calculation_basic_024_methyl_nitrate_no_bond_order；概括：计算 GFN2-xTB 水平下硝酸甲酯指定 N-O 单键的 Wiberg 键级。</x:v>
       </x:c>
-      <x:c r="B28" s="181" t="str">
+      <x:c r="B28" s="244" t="str">
         <x:v>±0.2</x:v>
       </x:c>
-      <x:c r="C28" s="181" t="str">
+      <x:c r="C28" s="244" t="str">
         <x:v>{"answer":0.9292,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D28" s="189" t="str">
+      <x:c r="D28" s="248" t="str">
         <x:v>{"answer":0.930,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E28" s="194" t="n">
+      <x:c r="E28" s="251" t="n">
         <x:v>0.9959999999999999</x:v>
       </x:c>
-      <x:c r="F28" s="189" t="str">
+      <x:c r="F28" s="248" t="str">
         <x:v>{"answer":0.9661815181817287,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G28" s="194" t="n">
+      <x:c r="G28" s="251" t="n">
         <x:v>0.8150924090913566</x:v>
       </x:c>
-      <x:c r="H28" s="189" t="str">
+      <x:c r="H28" s="248" t="str">
         <x:v>{"answer":0.93,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I28" s="194" t="n">
+      <x:c r="I28" s="251" t="n">
         <x:v>0.9959999999999999</x:v>
       </x:c>
-      <x:c r="J28" s="189" t="str">
+      <x:c r="J28" s="248" t="str">
         <x:v>{"answer":0.93,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K28" s="194" t="n">
+      <x:c r="K28" s="251" t="n">
         <x:v>0.9959999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="29" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A29" s="181" t="str">
+      <x:c r="A29" s="244" t="str">
         <x:v>property_calculation_basic_025_phenol_surface_esp_minimum；概括：计算 B3LYP/6-31G** 水平下苯酚范德华表面的最小静电势。</x:v>
       </x:c>
-      <x:c r="B29" s="181" t="str">
+      <x:c r="B29" s="244" t="str">
         <x:v>±5 kcal/mol</x:v>
       </x:c>
-      <x:c r="C29" s="181" t="str">
+      <x:c r="C29" s="244" t="str">
         <x:v>{"answer":-25.95,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D29" s="189" t="str">
+      <x:c r="D29" s="248" t="str">
         <x:v>{"answer":-32.7295,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E29" s="194" t="n">
+      <x:c r="E29" s="251" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="189" t="str">
+      <x:c r="F29" s="248" t="str">
         <x:v>{"answer":-26.0378553128,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G29" s="194" t="n">
+      <x:c r="G29" s="251" t="n">
         <x:v>0.9824289374399996</x:v>
       </x:c>
-      <x:c r="H29" s="189" t="str">
+      <x:c r="H29" s="248" t="str">
         <x:v>{"answer":-26.0,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I29" s="194" t="n">
+      <x:c r="I29" s="251" t="n">
         <x:v>0.9899999999999999</x:v>
       </x:c>
-      <x:c r="J29" s="189" t="str">
+      <x:c r="J29" s="248" t="str">
         <x:v>{"answer":-32.74,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K29" s="194" t="n">
+      <x:c r="K29" s="251" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A30" s="181" t="str">
+      <x:c r="A30" s="244" t="str">
         <x:v>property_calculation_basic_026_nitrobenzene_vdw_surface_area；概括：计算 B3LYP/6-31G** 水平下硝基苯的范德华表面积。</x:v>
       </x:c>
-      <x:c r="B30" s="181" t="str">
+      <x:c r="B30" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C30" s="181" t="str">
+      <x:c r="C30" s="244" t="str">
         <x:v>{"answer":150.3,"unit":"angstrom^2"}</x:v>
       </x:c>
-      <x:c r="D30" s="189" t="str">
+      <x:c r="D30" s="248" t="str">
         <x:v>{"answer":150.32,"unit":"angstrom^2"}</x:v>
       </x:c>
-      <x:c r="E30" s="194" t="n">
+      <x:c r="E30" s="251" t="n">
         <x:v>0.9986693280106466</x:v>
       </x:c>
-      <x:c r="F30" s="189" t="str">
+      <x:c r="F30" s="248" t="str">
         <x:v>{"answer":150.32,"unit":"angstrom^2"}</x:v>
       </x:c>
-      <x:c r="G30" s="194" t="n">
+      <x:c r="G30" s="251" t="n">
         <x:v>0.9986693280106466</x:v>
       </x:c>
-      <x:c r="H30" s="189" t="str">
+      <x:c r="H30" s="248" t="str">
         <x:v>{"answer":137.5,"unit":"angstrom^2"}</x:v>
       </x:c>
-      <x:c r="I30" s="194" t="n">
+      <x:c r="I30" s="251" t="n">
         <x:v>0.14836992681303984</x:v>
       </x:c>
-      <x:c r="J30" s="189" t="str">
+      <x:c r="J30" s="248" t="str">
         <x:v>{"answer":135.4,"unit":"angstrom^2"}</x:v>
       </x:c>
-      <x:c r="K30" s="194" t="n">
+      <x:c r="K30" s="251" t="n">
         <x:v>0.008649367930804619</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A31" s="181" t="str">
+      <x:c r="A31" s="244" t="str">
         <x:v>property_calculation_basic_027_pyrrole_surface_esp_variance；概括：计算 B3LYP/6-31G** 水平下吡咯范德华表面静电势的总方差。</x:v>
       </x:c>
-      <x:c r="B31" s="181" t="str">
+      <x:c r="B31" s="244" t="str">
         <x:v>±30%</x:v>
       </x:c>
-      <x:c r="C31" s="181" t="str">
+      <x:c r="C31" s="244" t="str">
         <x:v>{"answer":178.25,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
-      <x:c r="D31" s="189" t="str">
+      <x:c r="D31" s="248" t="str">
         <x:v>{"answer":179.75,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
-      <x:c r="E31" s="194" t="n">
+      <x:c r="E31" s="251" t="n">
         <x:v>0.9719495091164095</x:v>
       </x:c>
-      <x:c r="F31" s="189" t="str">
+      <x:c r="F31" s="248" t="str">
         <x:v>{"answer":179.75,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
-      <x:c r="G31" s="194" t="n">
+      <x:c r="G31" s="251" t="n">
         <x:v>0.9719495091164095</x:v>
       </x:c>
-      <x:c r="H31" s="189" t="str">
+      <x:c r="H31" s="248" t="str">
         <x:v>{"answer":231.4,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
-      <x:c r="I31" s="194" t="n">
+      <x:c r="I31" s="251" t="n">
         <x:v>0.006077606358111165</x:v>
       </x:c>
-      <x:c r="J31" s="189" t="str">
+      <x:c r="J31" s="248" t="str">
         <x:v>{"answer":323.6,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
-      <x:c r="K31" s="194" t="n">
+      <x:c r="K31" s="251" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A32" s="181" t="str">
+      <x:c r="A32" s="244" t="str">
         <x:v>property_calculation_basic_028_urea_crystal_density；概括：按指定分子晶体近似计算尿素晶体密度。</x:v>
       </x:c>
-      <x:c r="B32" s="181" t="str">
+      <x:c r="B32" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C32" s="181" t="str">
+      <x:c r="C32" s="244" t="str">
         <x:v>{"answer":1.333,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="D32" s="189" t="str">
+      <x:c r="D32" s="248" t="str">
         <x:v>{"answer":1.34923,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="E32" s="194" t="n">
+      <x:c r="E32" s="251" t="n">
         <x:v>0.8782445611402854</x:v>
       </x:c>
-      <x:c r="F32" s="189" t="str">
+      <x:c r="F32" s="248" t="str">
         <x:v>{"answer":1.349,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="G32" s="194" t="n">
+      <x:c r="G32" s="251" t="n">
         <x:v>0.8799699924981245</x:v>
       </x:c>
-      <x:c r="H32" s="189" t="str">
+      <x:c r="H32" s="248" t="str">
         <x:v>{"answer":1.353,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="I32" s="194" t="n">
+      <x:c r="I32" s="251" t="n">
         <x:v>0.8499624906226555</x:v>
       </x:c>
-      <x:c r="J32" s="189" t="str">
+      <x:c r="J32" s="248" t="str">
         <x:v>{"answer":1.349,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="K32" s="194" t="n">
+      <x:c r="K32" s="251" t="n">
         <x:v>0.8799699924981245</x:v>
       </x:c>
     </x:row>
     <x:row r="33" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A33" s="181" t="str">
+      <x:c r="A33" s="244" t="str">
         <x:v>property_calculation_basic_029_tnt_crystal_density；概括：按指定分子晶体近似计算 TNT 晶体密度。</x:v>
       </x:c>
-      <x:c r="B33" s="181" t="str">
+      <x:c r="B33" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C33" s="181" t="str">
+      <x:c r="C33" s="244" t="str">
         <x:v>{"answer":1.71,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="D33" s="189" t="str">
+      <x:c r="D33" s="248" t="str">
         <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="E33" s="194" t="n">
+      <x:c r="E33" s="251" t="n">
         <x:v>0.8830409356725145</x:v>
       </x:c>
-      <x:c r="F33" s="189" t="str">
+      <x:c r="F33" s="248" t="str">
         <x:v>{"answer":1.730,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="G33" s="194" t="n">
+      <x:c r="G33" s="251" t="n">
         <x:v>0.8830409356725145</x:v>
       </x:c>
-      <x:c r="H33" s="189" t="str">
+      <x:c r="H33" s="248" t="str">
         <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="I33" s="194" t="n">
+      <x:c r="I33" s="251" t="n">
         <x:v>0.8830409356725145</x:v>
       </x:c>
-      <x:c r="J33" s="189" t="str">
+      <x:c r="J33" s="248" t="str">
         <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="K33" s="194" t="n">
+      <x:c r="K33" s="251" t="n">
         <x:v>0.8830409356725145</x:v>
       </x:c>
     </x:row>
     <x:row r="34" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A34" s="181" t="str">
+      <x:c r="A34" s="244" t="str">
         <x:v>property_calculation_basic_030_picric_acid_crystal_density；概括：按指定分子晶体近似计算苦味酸晶体密度。</x:v>
       </x:c>
-      <x:c r="B34" s="181" t="str">
+      <x:c r="B34" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C34" s="181" t="str">
+      <x:c r="C34" s="244" t="str">
         <x:v>{"answer":1.831,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="D34" s="189" t="str">
+      <x:c r="D34" s="248" t="str">
         <x:v>{"answer":1.8508,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="E34" s="194" t="n">
+      <x:c r="E34" s="251" t="n">
         <x:v>0.8918623702894591</x:v>
       </x:c>
-      <x:c r="F34" s="189" t="str">
+      <x:c r="F34" s="248" t="str">
         <x:v>{"answer":1.8527,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="G34" s="194" t="n">
+      <x:c r="G34" s="251" t="n">
         <x:v>0.8814855270344072</x:v>
       </x:c>
-      <x:c r="H34" s="189" t="str">
+      <x:c r="H34" s="248" t="str">
         <x:v>{"answer":1.853,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="I34" s="194" t="n">
+      <x:c r="I34" s="251" t="n">
         <x:v>0.8798470780993991</x:v>
       </x:c>
-      <x:c r="J34" s="189" t="str">
+      <x:c r="J34" s="248" t="str">
         <x:v>{"answer":1.853,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="K34" s="194" t="n">
+      <x:c r="K34" s="251" t="n">
         <x:v>0.8798470780993991</x:v>
       </x:c>
     </x:row>
     <x:row r="35" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A35" s="181" t="str">
+      <x:c r="A35" s="244" t="str">
         <x:v>property_calculation_basic_031_allyl_radical_c1_spin_density；概括：计算 UB3LYP/6-31G* 水平下烯丙基自由基指定原子的自旋密度。</x:v>
       </x:c>
-      <x:c r="B35" s="181" t="str">
+      <x:c r="B35" s="244" t="str">
         <x:v>±0.2</x:v>
       </x:c>
-      <x:c r="C35" s="181" t="str">
+      <x:c r="C35" s="244" t="str">
         <x:v>{"answer":-0.266,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D35" s="189" t="str">
+      <x:c r="D35" s="248" t="str">
         <x:v>{"answer":-0.27486,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E35" s="194" t="n">
+      <x:c r="E35" s="251" t="n">
         <x:v>0.9557000000000001</x:v>
       </x:c>
-      <x:c r="F35" s="189" t="str">
+      <x:c r="F35" s="248" t="str">
         <x:v>{"answer":-0.274885,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G35" s="194" t="n">
+      <x:c r="G35" s="251" t="n">
         <x:v>0.9555750000000001</x:v>
       </x:c>
-      <x:c r="H35" s="189" t="str">
+      <x:c r="H35" s="248" t="str">
         <x:v>{"answer":-0.2748,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I35" s="194" t="n">
+      <x:c r="I35" s="251" t="n">
         <x:v>0.9560000000000002</x:v>
       </x:c>
-      <x:c r="J35" s="189" t="str">
+      <x:c r="J35" s="248" t="str">
         <x:v>{"answer":-0.27486,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K35" s="194" t="n">
+      <x:c r="K35" s="251" t="n">
         <x:v>0.9557000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="36" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A36" s="181" t="str">
+      <x:c r="A36" s="244" t="str">
         <x:v>property_calculation_basic_032_benzyl_radical_para_c_spin_density；概括：计算 UB3LYP/6-31G* 水平下苄基自由基对位碳的自旋密度。</x:v>
       </x:c>
-      <x:c r="B36" s="181" t="str">
+      <x:c r="B36" s="244" t="str">
         <x:v>±0.2</x:v>
       </x:c>
-      <x:c r="C36" s="181" t="str">
+      <x:c r="C36" s="244" t="str">
         <x:v>{"answer":0.301,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D36" s="189" t="str">
+      <x:c r="D36" s="248" t="str">
         <x:v>{"answer":0.284262,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E36" s="194" t="n">
+      <x:c r="E36" s="251" t="n">
         <x:v>0.9163100000000002</x:v>
       </x:c>
-      <x:c r="F36" s="189" t="str">
+      <x:c r="F36" s="248" t="str">
         <x:v>{"answer":0.284321053217,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G36" s="194" t="n">
+      <x:c r="G36" s="251" t="n">
         <x:v>0.9166052660850001</x:v>
       </x:c>
-      <x:c r="H36" s="189" t="str">
+      <x:c r="H36" s="248" t="str">
         <x:v>{"answer":0.2244,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I36" s="194" t="n">
+      <x:c r="I36" s="251" t="n">
         <x:v>0.617</x:v>
       </x:c>
-      <x:c r="J36" s="189" t="str">
+      <x:c r="J36" s="248" t="str">
         <x:v>{"answer":0.2842,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K36" s="194" t="n">
+      <x:c r="K36" s="251" t="n">
         <x:v>0.9160000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="37" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A37" s="181" t="str">
+      <x:c r="A37" s="244" t="str">
         <x:v>property_calculation_basic_033_phenoxy_radical_o_spin_density；概括：计算 UB3LYP/6-31G* 水平下苯氧自由基氧原子的自旋密度。</x:v>
       </x:c>
-      <x:c r="B37" s="181" t="str">
+      <x:c r="B37" s="244" t="str">
         <x:v>±0.2</x:v>
       </x:c>
-      <x:c r="C37" s="181" t="str">
+      <x:c r="C37" s="244" t="str">
         <x:v>{"answer":0.415,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D37" s="189" t="str">
+      <x:c r="D37" s="248" t="str">
         <x:v>{"answer":0.44484621905874866,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E37" s="194" t="n">
+      <x:c r="E37" s="251" t="n">
         <x:v>0.8507689047062565</x:v>
       </x:c>
-      <x:c r="F37" s="189" t="str">
+      <x:c r="F37" s="248" t="str">
         <x:v>{"answer":0.6829546990237992,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G37" s="194" t="n">
+      <x:c r="G37" s="251" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H37" s="189" t="str">
+      <x:c r="H37" s="248" t="str">
         <x:v>{"answer":0.445,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I37" s="194" t="n">
+      <x:c r="I37" s="251" t="n">
         <x:v>0.8499999999999999</x:v>
       </x:c>
-      <x:c r="J37" s="189" t="str">
+      <x:c r="J37" s="248" t="str">
         <x:v>{"answer":0.4449,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K37" s="194" t="n">
+      <x:c r="K37" s="251" t="n">
         <x:v>0.8504999999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="38" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A38" s="181" t="str">
+      <x:c r="A38" s="244" t="str">
         <x:v>property_calculation_basic_034_indole_c3_fukui_minus；概括：计算 GFN2-xTB 水平下吲哚 C3 位的 f- Fukui 函数。</x:v>
       </x:c>
-      <x:c r="B38" s="181" t="str">
+      <x:c r="B38" s="244" t="str">
         <x:v>±0.05</x:v>
       </x:c>
-      <x:c r="C38" s="181" t="str">
+      <x:c r="C38" s="244" t="str">
         <x:v>{"answer":0.076,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D38" s="189" t="str">
+      <x:c r="D38" s="248" t="str">
         <x:v>{"answer":0.076,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E38" s="194" t="n">
+      <x:c r="E38" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F38" s="189" t="str">
+      <x:c r="F38" s="248" t="str">
         <x:v>{"answer":0.076,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G38" s="194" t="n">
+      <x:c r="G38" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H38" s="189" t="str">
+      <x:c r="H38" s="248" t="str">
         <x:v>{"answer":0.076,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I38" s="194" t="n">
+      <x:c r="I38" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J38" s="189" t="str">
+      <x:c r="J38" s="248" t="str">
         <x:v>{"answer":0.0759,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K38" s="194" t="n">
+      <x:c r="K38" s="251" t="n">
         <x:v>0.998</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A39" s="181" t="str">
+      <x:c r="A39" s="244" t="str">
         <x:v>property_calculation_basic_035_chloronitrobenzene_c_fukui_plus；概括：计算 GFN2-xTB 水平下氯硝基苯指定碳原子的 f+ Fukui 函数。</x:v>
       </x:c>
-      <x:c r="B39" s="181" t="str">
+      <x:c r="B39" s="244" t="str">
         <x:v>±0.05</x:v>
       </x:c>
-      <x:c r="C39" s="181" t="str">
+      <x:c r="C39" s="244" t="str">
         <x:v>{"answer":0.055,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D39" s="189" t="str">
+      <x:c r="D39" s="248" t="str">
         <x:v>{"answer":0.055,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E39" s="194" t="n">
+      <x:c r="E39" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F39" s="189" t="str">
+      <x:c r="F39" s="248" t="str">
         <x:v>{"answer":0.055,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G39" s="194" t="n">
+      <x:c r="G39" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H39" s="189" t="str">
+      <x:c r="H39" s="248" t="str">
         <x:v>{"answer":0.055,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I39" s="194" t="n">
+      <x:c r="I39" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J39" s="189" t="str">
+      <x:c r="J39" s="248" t="str">
         <x:v>{"answer":0.0539,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K39" s="194" t="n">
+      <x:c r="K39" s="251" t="n">
         <x:v>0.9780000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="40" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A40" s="181" t="str">
+      <x:c r="A40" s="244" t="str">
         <x:v>property_calculation_basic_036_furfural_carbonyl_c_fukui_plus；概括：计算 GFN2-xTB 水平下糠醛羰基碳的 f+ Fukui 函数。</x:v>
       </x:c>
-      <x:c r="B40" s="181" t="str">
+      <x:c r="B40" s="244" t="str">
         <x:v>±0.05</x:v>
       </x:c>
-      <x:c r="C40" s="181" t="str">
+      <x:c r="C40" s="244" t="str">
         <x:v>{"answer":0.07,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="D40" s="189" t="str">
+      <x:c r="D40" s="248" t="str">
         <x:v>{"answer":0.070,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="E40" s="194" t="n">
+      <x:c r="E40" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F40" s="189" t="str">
+      <x:c r="F40" s="248" t="str">
         <x:v>{"answer":0.070,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="G40" s="194" t="n">
+      <x:c r="G40" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H40" s="189" t="str">
+      <x:c r="H40" s="248" t="str">
         <x:v>{"answer":0.069,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="I40" s="194" t="n">
+      <x:c r="I40" s="251" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="J40" s="189" t="str">
+      <x:c r="J40" s="248" t="str">
         <x:v>{"answer":0.069,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K40" s="194" t="n">
+      <x:c r="K40" s="251" t="n">
         <x:v>0.98</x:v>
       </x:c>
     </x:row>
     <x:row r="41" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A41" s="181" t="str">
+      <x:c r="A41" s="244" t="str">
         <x:v>property_calculation_basic_037_benzene_standard_entropy；概括：计算气相苯在 298.15 K 的标准摩尔熵。</x:v>
       </x:c>
-      <x:c r="B41" s="181" t="str">
+      <x:c r="B41" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C41" s="181" t="str">
+      <x:c r="C41" s="244" t="str">
         <x:v>{"answer":64.67,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="D41" s="189" t="str">
+      <x:c r="D41" s="248" t="str">
         <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="E41" s="194" t="n">
+      <x:c r="E41" s="251" t="n">
         <x:v>0.9489717024895626</x:v>
       </x:c>
-      <x:c r="F41" s="189" t="str">
+      <x:c r="F41" s="248" t="str">
         <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="G41" s="194" t="n">
+      <x:c r="G41" s="251" t="n">
         <x:v>0.9489717024895626</x:v>
       </x:c>
-      <x:c r="H41" s="189" t="str">
+      <x:c r="H41" s="248" t="str">
         <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="I41" s="194" t="n">
+      <x:c r="I41" s="251" t="n">
         <x:v>0.9489717024895626</x:v>
       </x:c>
-      <x:c r="J41" s="189" t="str">
+      <x:c r="J41" s="248" t="str">
         <x:v>{"answer":64.37,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="K41" s="194" t="n">
+      <x:c r="K41" s="251" t="n">
         <x:v>0.9536106386268753</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A42" s="181" t="str">
+      <x:c r="A42" s="244" t="str">
         <x:v>property_calculation_basic_038_acetonitrile_standard_entropy；概括：计算气相乙腈在 298.15 K 的标准摩尔熵。</x:v>
       </x:c>
-      <x:c r="B42" s="181" t="str">
+      <x:c r="B42" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C42" s="181" t="str">
+      <x:c r="C42" s="244" t="str">
         <x:v>{"answer":57.88,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="D42" s="189" t="str">
+      <x:c r="D42" s="248" t="str">
         <x:v>{"answer":58.04,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="E42" s="194" t="n">
+      <x:c r="E42" s="251" t="n">
         <x:v>0.9723565998617836</x:v>
       </x:c>
-      <x:c r="F42" s="189" t="str">
+      <x:c r="F42" s="248" t="str">
         <x:v>{"answer":58.01,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="G42" s="194" t="n">
+      <x:c r="G42" s="251" t="n">
         <x:v>0.9775397373876995</x:v>
       </x:c>
-      <x:c r="H42" s="189" t="str">
+      <x:c r="H42" s="248" t="str">
         <x:v>{"answer":57.88,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="I42" s="194" t="n">
+      <x:c r="I42" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J42" s="189" t="str">
+      <x:c r="J42" s="248" t="str">
         <x:v>{"answer":58.17,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="K42" s="194" t="n">
+      <x:c r="K42" s="251" t="n">
         <x:v>0.9498963372494819</x:v>
       </x:c>
     </x:row>
     <x:row r="43" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A43" s="181" t="str">
+      <x:c r="A43" s="244" t="str">
         <x:v>property_calculation_basic_039_neopentane_standard_entropy；概括：计算气相新戊烷在 298.15 K 的标准摩尔熵。</x:v>
       </x:c>
-      <x:c r="B43" s="181" t="str">
+      <x:c r="B43" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C43" s="181" t="str">
+      <x:c r="C43" s="244" t="str">
         <x:v>{"answer":73.88,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="D43" s="189" t="str">
+      <x:c r="D43" s="248" t="str">
         <x:v>{"answer":73.14,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="E43" s="194" t="n">
+      <x:c r="E43" s="251" t="n">
         <x:v>0.8998375744450468</x:v>
       </x:c>
-      <x:c r="F43" s="189" t="str">
+      <x:c r="F43" s="248" t="str">
         <x:v>{"answer":75.22,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="G43" s="194" t="n">
+      <x:c r="G43" s="251" t="n">
         <x:v>0.8186247969680558</x:v>
       </x:c>
-      <x:c r="H43" s="189" t="str">
+      <x:c r="H43" s="248" t="str">
         <x:v>{"answer":73.85,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="I43" s="194" t="n">
+      <x:c r="I43" s="251" t="n">
         <x:v>0.9959393611261503</x:v>
       </x:c>
-      <x:c r="J43" s="189" t="str">
+      <x:c r="J43" s="248" t="str">
         <x:v>{"answer":73.5,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="K43" s="194" t="n">
+      <x:c r="K43" s="251" t="n">
         <x:v>0.9485652409312405</x:v>
       </x:c>
     </x:row>
     <x:row r="44" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A44" s="181" t="str">
+      <x:c r="A44" s="244" t="str">
         <x:v>property_calculation_basic_040_methane_standard_entropy；概括：计算气相甲烷在 298.15 K 的标准摩尔熵。</x:v>
       </x:c>
-      <x:c r="B44" s="181" t="str">
+      <x:c r="B44" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C44" s="181" t="str">
+      <x:c r="C44" s="244" t="str">
         <x:v>{"answer":44.4,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="D44" s="189" t="str">
+      <x:c r="D44" s="248" t="str">
         <x:v>{"answer":44.52,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="E44" s="194" t="n">
+      <x:c r="E44" s="251" t="n">
         <x:v>0.9729729729729719</x:v>
       </x:c>
-      <x:c r="F44" s="189" t="str">
+      <x:c r="F44" s="248" t="str">
         <x:v>{"answer":44.516,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="G44" s="194" t="n">
+      <x:c r="G44" s="251" t="n">
         <x:v>0.9738738738738739</x:v>
       </x:c>
-      <x:c r="H44" s="189" t="str">
+      <x:c r="H44" s="248" t="str">
         <x:v>{"answer":44.5,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="I44" s="194" t="n">
+      <x:c r="I44" s="251" t="n">
         <x:v>0.9774774774774772</x:v>
       </x:c>
-      <x:c r="J44" s="189" t="str">
+      <x:c r="J44" s="248" t="str">
         <x:v>{"answer":44.52,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="K44" s="194" t="n">
+      <x:c r="K44" s="251" t="n">
         <x:v>0.9729729729729719</x:v>
       </x:c>
     </x:row>
     <x:row r="45" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A45" s="181" t="str">
+      <x:c r="A45" s="244" t="str">
         <x:v>property_calculation_basic_041_ammonia_standard_entropy；概括：计算气相氨在 298.15 K 的标准摩尔熵。</x:v>
       </x:c>
-      <x:c r="B45" s="181" t="str">
+      <x:c r="B45" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C45" s="181" t="str">
+      <x:c r="C45" s="244" t="str">
         <x:v>{"answer":45.92,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="D45" s="189" t="str">
+      <x:c r="D45" s="248" t="str">
         <x:v>{"answer":46.073136,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="E45" s="194" t="n">
+      <x:c r="E45" s="251" t="n">
         <x:v>0.9666515679442517</x:v>
       </x:c>
-      <x:c r="F45" s="189" t="str">
+      <x:c r="F45" s="248" t="str">
         <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="G45" s="194" t="n">
+      <x:c r="G45" s="251" t="n">
         <x:v>0.9673344947735195</x:v>
       </x:c>
-      <x:c r="H45" s="189" t="str">
+      <x:c r="H45" s="248" t="str">
         <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="I45" s="194" t="n">
+      <x:c r="I45" s="251" t="n">
         <x:v>0.9673344947735195</x:v>
       </x:c>
-      <x:c r="J45" s="189" t="str">
+      <x:c r="J45" s="248" t="str">
         <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="K45" s="194" t="n">
+      <x:c r="K45" s="251" t="n">
         <x:v>0.9673344947735195</x:v>
       </x:c>
     </x:row>
     <x:row r="46" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A46" s="181" t="str">
+      <x:c r="A46" s="244" t="str">
         <x:v>property_calculation_basic_042_carbon_dioxide_standard_entropy；概括：计算气相二氧化碳在 298.15 K 的标准摩尔熵。</x:v>
       </x:c>
-      <x:c r="B46" s="181" t="str">
+      <x:c r="B46" s="244" t="str">
         <x:v>±10%</x:v>
       </x:c>
-      <x:c r="C46" s="181" t="str">
+      <x:c r="C46" s="244" t="str">
         <x:v>{"answer":51.18,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="D46" s="189" t="str">
+      <x:c r="D46" s="248" t="str">
         <x:v>{"answer":51.095841,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="E46" s="194" t="n">
+      <x:c r="E46" s="251" t="n">
         <x:v>0.9835562719812427</x:v>
       </x:c>
-      <x:c r="F46" s="189" t="str">
+      <x:c r="F46" s="248" t="str">
         <x:v>{"answer":51.10,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="G46" s="194" t="n">
+      <x:c r="G46" s="251" t="n">
         <x:v>0.9843688940992579</x:v>
       </x:c>
-      <x:c r="H46" s="189" t="str">
+      <x:c r="H46" s="248" t="str">
         <x:v>{"answer":51.1,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="I46" s="194" t="n">
+      <x:c r="I46" s="251" t="n">
         <x:v>0.9843688940992579</x:v>
       </x:c>
-      <x:c r="J46" s="189" t="str">
+      <x:c r="J46" s="248" t="str">
         <x:v>{"answer":51.1,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="K46" s="194" t="n">
+      <x:c r="K46" s="251" t="n">
         <x:v>0.9843688940992579</x:v>
       </x:c>
     </x:row>
     <x:row r="47" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A47" s="181" t="str">
+      <x:c r="A47" s="244" t="str">
         <x:v>property_calculation_basic_043_acetic_acid_dimerization_enthalpy；概括：计算 GFN2-xTB 水平下乙酸环状二聚体在 298.15 K 的二聚焓并保留符号。</x:v>
       </x:c>
-      <x:c r="B47" s="181" t="str">
+      <x:c r="B47" s="244" t="str">
         <x:v>±3 kcal/mol</x:v>
       </x:c>
-      <x:c r="C47" s="181" t="str">
+      <x:c r="C47" s="244" t="str">
         <x:v>{"answer":-16.04,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="D47" s="189" t="str">
+      <x:c r="D47" s="248" t="str">
         <x:v>{"answer":-16.0426,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="E47" s="194" t="n">
+      <x:c r="E47" s="251" t="n">
         <x:v>0.999133333333333</x:v>
       </x:c>
-      <x:c r="F47" s="189" t="str">
+      <x:c r="F47" s="248" t="str">
         <x:v>{"answer":-16.04,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="G47" s="194" t="n">
+      <x:c r="G47" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H47" s="189" t="str">
+      <x:c r="H47" s="248" t="str">
         <x:v>{"answer":-16.13,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="I47" s="194" t="n">
+      <x:c r="I47" s="251" t="n">
         <x:v>0.9700000000000001</x:v>
       </x:c>
-      <x:c r="J47" s="189" t="str">
+      <x:c r="J47" s="248" t="str">
         <x:v>{"answer":-17.2,"unit":"kcal/mol"}</x:v>
       </x:c>
-      <x:c r="K47" s="194" t="n">
+      <x:c r="K47" s="251" t="n">
         <x:v>0.6133333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="48" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A48" s="181" t="str">
+      <x:c r="A48" s="244" t="str">
         <x:v>property_calculation_basic_044_caffeine_most_negative_mulliken_atom；概括：识别 GFN2-xTB 水平下咖啡因中 Mulliken 电荷最负的原子。</x:v>
       </x:c>
-      <x:c r="B48" s="181" t="str">
+      <x:c r="B48" s="244" t="str">
         <x:v>原子身份匹配</x:v>
       </x:c>
-      <x:c r="C48" s="181" t="str">
+      <x:c r="C48" s="244" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
-      <x:c r="D48" s="189" t="str">
+      <x:c r="D48" s="248" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
-      <x:c r="E48" s="194" t="n">
+      <x:c r="E48" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F48" s="189" t="str">
+      <x:c r="F48" s="248" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
-      <x:c r="G48" s="194" t="n">
+      <x:c r="G48" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H48" s="189" t="str">
+      <x:c r="H48" s="248" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
-      <x:c r="I48" s="194" t="n">
+      <x:c r="I48" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J48" s="189" t="str">
+      <x:c r="J48" s="248" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
-      <x:c r="K48" s="194" t="n">
+      <x:c r="K48" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="49" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A49" s="181" t="str">
+      <x:c r="A49" s="244" t="str">
         <x:v>property_calculation_basic_045_trifluoroacetic_acid_hydrogen_charge；概括：计算 GFN2-xTB 水平下三氟乙酸羧基氢的 Mulliken 电荷。</x:v>
       </x:c>
-      <x:c r="B49" s="181" t="str">
+      <x:c r="B49" s="244" t="str">
         <x:v>±0.15 e</x:v>
       </x:c>
-      <x:c r="C49" s="181" t="str">
+      <x:c r="C49" s="244" t="str">
         <x:v>{"answer":0.364,"unit":"e"}</x:v>
       </x:c>
-      <x:c r="D49" s="189" t="str">
+      <x:c r="D49" s="248" t="str">
         <x:v>{"answer":0.36363323,"unit":"e"}</x:v>
       </x:c>
-      <x:c r="E49" s="194" t="n">
+      <x:c r="E49" s="251" t="n">
         <x:v>0.9975548666666666</x:v>
       </x:c>
-      <x:c r="F49" s="189" t="str">
+      <x:c r="F49" s="248" t="str">
         <x:v>{"answer":0.3636,"unit":"e"}</x:v>
       </x:c>
-      <x:c r="G49" s="194" t="n">
+      <x:c r="G49" s="251" t="n">
         <x:v>0.9973333333333333</x:v>
       </x:c>
-      <x:c r="H49" s="189" t="str">
+      <x:c r="H49" s="248" t="str">
         <x:v>{"answer":0.3637,"unit":"e"}</x:v>
       </x:c>
-      <x:c r="I49" s="194" t="n">
+      <x:c r="I49" s="251" t="n">
         <x:v>0.9980000000000002</x:v>
       </x:c>
-      <x:c r="J49" s="189" t="str">
+      <x:c r="J49" s="248" t="str">
         <x:v>{"answer":0.364,"unit":"e"}</x:v>
       </x:c>
-      <x:c r="K49" s="194" t="n">
+      <x:c r="K49" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A50" s="181" t="str">
+      <x:c r="A50" s="244" t="str">
         <x:v>property_calculation_basic_046_methyl_azide_most_negative_mulliken_atom；概括：识别 GFN2-xTB 水平下叠氮甲烷中 Mulliken 电荷最负的氮原子。</x:v>
       </x:c>
-      <x:c r="B50" s="181" t="str">
+      <x:c r="B50" s="244" t="str">
         <x:v>原子身份匹配</x:v>
       </x:c>
-      <x:c r="C50" s="181" t="str">
+      <x:c r="C50" s="244" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
-      <x:c r="D50" s="189" t="str">
+      <x:c r="D50" s="248" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
-      <x:c r="E50" s="194" t="n">
+      <x:c r="E50" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F50" s="189" t="str">
+      <x:c r="F50" s="248" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
-      <x:c r="G50" s="194" t="n">
+      <x:c r="G50" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H50" s="189" t="str">
+      <x:c r="H50" s="248" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
-      <x:c r="I50" s="194" t="n">
+      <x:c r="I50" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J50" s="189" t="str">
+      <x:c r="J50" s="248" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
-      <x:c r="K50" s="194" t="n">
+      <x:c r="K50" s="251" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A51" s="181" t="str">
+      <x:c r="A51" s="244" t="str">
         <x:v>property_calculation_basic_047_formaldehyde_s1_vertical_excitation_energy；概括：计算 RI-TDA-B3LYP/def2-SVP 水平下甲醛的 S1 垂直激发能。</x:v>
       </x:c>
-      <x:c r="B51" s="181" t="str">
+      <x:c r="B51" s="244" t="str">
         <x:v>±0.5 eV</x:v>
       </x:c>
-      <x:c r="C51" s="181" t="str">
+      <x:c r="C51" s="244" t="str">
         <x:v>{"answer":4.12,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="D51" s="189" t="str">
+      <x:c r="D51" s="248" t="str">
         <x:v>{"answer":4.078,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="E51" s="194" t="n">
+      <x:c r="E51" s="251" t="n">
         <x:v>0.9160000000000004</x:v>
       </x:c>
-      <x:c r="F51" s="189" t="str">
+      <x:c r="F51" s="248" t="str">
         <x:v>{"answer":4.08,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="G51" s="194" t="n">
+      <x:c r="G51" s="251" t="n">
         <x:v>0.9199999999999999</x:v>
       </x:c>
-      <x:c r="H51" s="189" t="str">
+      <x:c r="H51" s="248" t="str">
         <x:v>{"answer":4.078,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="I51" s="194" t="n">
+      <x:c r="I51" s="251" t="n">
         <x:v>0.9160000000000004</x:v>
       </x:c>
-      <x:c r="J51" s="189" t="str">
+      <x:c r="J51" s="248" t="str">
         <x:v>{"answer":4.08,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="K51" s="194" t="n">
+      <x:c r="K51" s="251" t="n">
         <x:v>0.9199999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="52" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A52" s="181" t="str">
+      <x:c r="A52" s="244" t="str">
         <x:v>property_calculation_basic_048_acetaldehyde_s1_vertical_excitation_energy；概括：计算 RI-TDA-B3LYP/def2-SVP 水平下乙醛的 S1 垂直激发能。</x:v>
       </x:c>
-      <x:c r="B52" s="181" t="str">
+      <x:c r="B52" s="244" t="str">
         <x:v>±0.5 eV</x:v>
       </x:c>
-      <x:c r="C52" s="181" t="str">
+      <x:c r="C52" s="244" t="str">
         <x:v>{"answer":4.42,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="D52" s="189" t="str">
+      <x:c r="D52" s="248" t="str">
         <x:v>{"answer":4.3656,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="E52" s="194" t="n">
+      <x:c r="E52" s="251" t="n">
         <x:v>0.8911999999999995</x:v>
       </x:c>
-      <x:c r="F52" s="189" t="str">
+      <x:c r="F52" s="248" t="str">
         <x:v>{"answer":4.3655,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="G52" s="194" t="n">
+      <x:c r="G52" s="251" t="n">
         <x:v>0.891</x:v>
       </x:c>
-      <x:c r="H52" s="189" t="str">
+      <x:c r="H52" s="248" t="str">
         <x:v>{"answer":4.37,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="I52" s="194" t="n">
+      <x:c r="I52" s="251" t="n">
         <x:v>0.9000000000000004</x:v>
       </x:c>
-      <x:c r="J52" s="189" t="str">
+      <x:c r="J52" s="248" t="str">
         <x:v>{"answer":4.3657,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="K52" s="194" t="n">
+      <x:c r="K52" s="251" t="n">
         <x:v>0.8914000000000009</x:v>
       </x:c>
     </x:row>
     <x:row r="53" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A53" s="181" t="str">
+      <x:c r="A53" s="244" t="str">
         <x:v>property_calculation_basic_049_acetone_s1_vertical_excitation_energy；概括：计算 RI-TDA-B3LYP/def2-SVP 水平下丙酮的 S1 垂直激发能。</x:v>
       </x:c>
-      <x:c r="B53" s="181" t="str">
+      <x:c r="B53" s="244" t="str">
         <x:v>±0.5 eV</x:v>
       </x:c>
-      <x:c r="C53" s="181" t="str">
+      <x:c r="C53" s="244" t="str">
         <x:v>{"answer":4.51,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="D53" s="189" t="str">
+      <x:c r="D53" s="248" t="str">
         <x:v>{"answer":4.4488,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="E53" s="194" t="n">
+      <x:c r="E53" s="251" t="n">
         <x:v>0.877600000000001</x:v>
       </x:c>
-      <x:c r="F53" s="189" t="str">
+      <x:c r="F53" s="248" t="str">
         <x:v>{"answer":4.44869,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="G53" s="194" t="n">
+      <x:c r="G53" s="251" t="n">
         <x:v>0.8773800000000005</x:v>
       </x:c>
-      <x:c r="H53" s="189" t="str">
+      <x:c r="H53" s="248" t="str">
         <x:v>{"answer":4.449,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="I53" s="194" t="n">
+      <x:c r="I53" s="251" t="n">
         <x:v>0.8780000000000001</x:v>
       </x:c>
-      <x:c r="J53" s="189" t="str">
+      <x:c r="J53" s="248" t="str">
         <x:v>{"answer":4.449,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="K53" s="194" t="n">
+      <x:c r="K53" s="251" t="n">
         <x:v>0.8780000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="54" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A54" s="181" t="str">
+      <x:c r="A54" s="244" t="str">
         <x:v>property_calculation_basic_050_pyrazine_s1_vertical_excitation_energy；概括：计算 RI-TDA-B3LYP/def2-SVP 水平下吡嗪的 S1 垂直激发能。</x:v>
       </x:c>
-      <x:c r="B54" s="181" t="str">
+      <x:c r="B54" s="244" t="str">
         <x:v>±0.5 eV</x:v>
       </x:c>
-      <x:c r="C54" s="181" t="str">
+      <x:c r="C54" s="244" t="str">
         <x:v>{"answer":4.04,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="D54" s="189" t="str">
+      <x:c r="D54" s="248" t="str">
         <x:v>{"answer":4.001,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="E54" s="194" t="n">
+      <x:c r="E54" s="251" t="n">
         <x:v>0.9220000000000006</x:v>
       </x:c>
-      <x:c r="F54" s="189" t="str">
+      <x:c r="F54" s="248" t="str">
         <x:v>{"answer":4.001,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="G54" s="194" t="n">
+      <x:c r="G54" s="251" t="n">
         <x:v>0.9220000000000006</x:v>
       </x:c>
-      <x:c r="H54" s="189" t="str">
+      <x:c r="H54" s="248" t="str">
         <x:v>{"answer":3.86,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="I54" s="194" t="n">
+      <x:c r="I54" s="251" t="n">
         <x:v>0.6399999999999997</x:v>
       </x:c>
-      <x:c r="J54" s="189" t="str">
+      <x:c r="J54" s="248" t="str">
         <x:v>{"answer":4.001,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="K54" s="194" t="n">
+      <x:c r="K54" s="251" t="n">
         <x:v>0.9220000000000006</x:v>
       </x:c>
     </x:row>
     <x:row r="55" s="123" customFormat="1" ht="76" customHeight="1">
-      <x:c r="A55" s="181" t="str">
+      <x:c r="A55" s="244" t="str">
         <x:v>property_calculation_basic_051_formaldehyde_t1_vertical_excitation_energy；概括：计算 RI-TDA-B3LYP/def2-SVP 水平下甲醛的 T1 垂直激发能。</x:v>
       </x:c>
-      <x:c r="B55" s="181" t="str">
+      <x:c r="B55" s="244" t="str">
         <x:v>±0.5 eV</x:v>
       </x:c>
-      <x:c r="C55" s="181" t="str">
+      <x:c r="C55" s="244" t="str">
         <x:v>{"answer":3.39,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="D55" s="189" t="str">
+      <x:c r="D55" s="248" t="str">
         <x:v>{"answer":3.36,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="E55" s="194" t="n">
+      <x:c r="E55" s="251" t="n">
         <x:v>0.9399999999999995</x:v>
       </x:c>
-      <x:c r="F55" s="189" t="str">
+      <x:c r="F55" s="248" t="str">
         <x:v>{"answer":3.36,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="G55" s="194" t="n">
+      <x:c r="G55" s="251" t="n">
         <x:v>0.9399999999999995</x:v>
       </x:c>
-      <x:c r="H55" s="189" t="str">
+      <x:c r="H55" s="248" t="str">
         <x:v>{"answer":3.358,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="I55" s="194" t="n">
+      <x:c r="I55" s="251" t="n">
         <x:v>0.9359999999999999</x:v>
       </x:c>
-      <x:c r="J55" s="189" t="str">
+      <x:c r="J55" s="248" t="str">
         <x:v>{"answer":3.357,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="K55" s="194" t="n">
+      <x:c r="K55" s="251" t="n">
         <x:v>0.9340000000000002</x:v>
       </x:c>
     </x:row>
     <x:row r="56" s="123" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A56" s="207" t="str">
+      <x:c r="A56" s="254" t="str">
         <x:v>各实验组平均分（忽略未评分项）</x:v>
       </x:c>
-      <x:c r="B56" s="214"/>
-      <x:c r="C56" s="214"/>
-      <x:c r="D56" s="213" t="str">
+      <x:c r="B56" s="257"/>
+      <x:c r="C56" s="257"/>
+      <x:c r="D56" s="260" t="str">
         <x:v>平均分</x:v>
       </x:c>
-      <x:c r="E56" s="213" t="n">
+      <x:c r="E56" s="260" t="n">
         <x:v>0.8779703257112016</x:v>
       </x:c>
-      <x:c r="F56" s="213" t="str">
+      <x:c r="F56" s="260" t="str">
         <x:v>平均分</x:v>
       </x:c>
-      <x:c r="G56" s="213" t="n">
+      <x:c r="G56" s="260" t="n">
         <x:v>0.8959689877559688</x:v>
       </x:c>
-      <x:c r="H56" s="213" t="str">
+      <x:c r="H56" s="260" t="str">
         <x:v>平均分</x:v>
       </x:c>
-      <x:c r="I56" s="213" t="n">
+      <x:c r="I56" s="260" t="n">
         <x:v>0.8728266900232937</x:v>
       </x:c>
-      <x:c r="J56" s="213" t="str">
+      <x:c r="J56" s="260" t="str">
         <x:v>平均分</x:v>
       </x:c>
-      <x:c r="K56" s="213" t="n">
+      <x:c r="K56" s="260" t="n">
         <x:v>0.8681871748566278</x:v>
       </x:c>
     </x:row>
